--- a/AP_튜브라인_계획실적_대조_LOSS산정.xlsx
+++ b/AP_튜브라인_계획실적_대조_LOSS산정.xlsx
@@ -798,19 +798,19 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>35주 (8/17~8/22)</t>
+          <t>34주 (8/17~8/22)</t>
         </is>
       </c>
       <c r="B6" s="6">
-        <f>SUMIFS('2.일별대조'!$G$4:$G$87,'2.일별대조'!$B$4:$B$87,35)</f>
+        <f>SUMIFS('2.일별대조'!$G$4:$G$87,'2.일별대조'!$B$4:$B$87,34)</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>SUMIFS('2.일별대조'!$H$4:$H$87,'2.일별대조'!$B$4:$B$87,35)</f>
+        <f>SUMIFS('2.일별대조'!$H$4:$H$87,'2.일별대조'!$B$4:$B$87,34)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>SUMIFS('2.일별대조'!$I$4:$I$87,'2.일별대조'!$B$4:$B$87,35)</f>
+        <f>SUMIFS('2.일별대조'!$I$4:$I$87,'2.일별대조'!$B$4:$B$87,34)</f>
         <v/>
       </c>
       <c r="E6" s="6">
@@ -829,19 +829,19 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>36주 (8/24~8/29)</t>
+          <t>35주 (8/24~8/29)  ← 당주</t>
         </is>
       </c>
       <c r="B7" s="6">
-        <f>SUMIFS('2.일별대조'!$G$4:$G$87,'2.일별대조'!$B$4:$B$87,36)</f>
+        <f>SUMIFS('2.일별대조'!$G$4:$G$87,'2.일별대조'!$B$4:$B$87,35)</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>SUMIFS('2.일별대조'!$H$4:$H$87,'2.일별대조'!$B$4:$B$87,36)</f>
+        <f>SUMIFS('2.일별대조'!$H$4:$H$87,'2.일별대조'!$B$4:$B$87,35)</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>SUMIFS('2.일별대조'!$I$4:$I$87,'2.일별대조'!$B$4:$B$87,36)</f>
+        <f>SUMIFS('2.일별대조'!$I$4:$I$87,'2.일별대조'!$B$4:$B$87,35)</f>
         <v/>
       </c>
       <c r="E7" s="6">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="B27" s="18">
-        <f>IF($B$25=0,"데이터 미입력 — [2.일별대조] 입력 필요",IF($B$21/$B$25&gt;=0.6,"A. 원청(포장재) 귀책 우세 → 정산 청구 근거 확보. AP 회신 시 결품 이력 첨부",IF($B$22/$B$25&gt;=0.4,"C. 도급 귀책 우세 → 방어 불가. 즉시 잔업·교대 복원 계획 제출","B. 혼재 → 공통 LOSS 사유별 재분류 후 재판정")))</f>
+        <f>IF($B$25=0,"데이터 미입력 — 2.일별대조 시트 입력 필요",IF($B$21/$B$25&gt;=0.6,"A. 원청(포장재) 귀책 우세 → 정산 청구 근거 확보. AP 회신 시 결품 이력 첨부",IF($B$22/$B$25&gt;=0.4,"C. 도급 귀책 우세 → 방어 불가. 즉시 잔업·교대 복원 계획 제출","B. 혼재 → 공통 LOSS 사유별 재분류 후 재판정")))</f>
         <v/>
       </c>
     </row>
